--- a/physician_forms/004_influenza_questionnaire--physician_forms.xlsx
+++ b/physician_forms/004_influenza_questionnaire--physician_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>flu_symptoms</t>
+          <t>flu_symptoms_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Flu Symptoms</t>
+          <t>Flu Symptoms 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Health Care Worker Contact</t>
+          <t>Healthcare Workplace Contact</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>healthcare_workplace</t>
+          <t>healthcare_workplace_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Health Care Workplace</t>
+          <t>Healthcare Workplace 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C114"/>
+  <dimension ref="A1:C112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sore_throat</t>
+          <t>nausea/vomiting</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sore Throat</t>
+          <t>Nausea/Vomiting</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nausea/vomiting</t>
+          <t>diarrhea</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Nausea/Vomiting</t>
+          <t>Diarrhea</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>diarrhea</t>
+          <t>confusion/disorientation</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Diarrhea</t>
+          <t>Confusion/Disorientation</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>confusion/disorientation</t>
+          <t>loss_of_appetite</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Confusion/Disorientation</t>
+          <t>Loss of Appetite</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>loss_of_appetite</t>
+          <t>loss_of_taste</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Loss of Appetite</t>
+          <t>Loss of Taste</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>loss_of_taste</t>
+          <t>loss_of_smell</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Loss of Taste</t>
+          <t>Loss of Smell</t>
         </is>
       </c>
     </row>
@@ -1522,29 +1522,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>loss_of_smell</t>
+          <t>loss_of_hearing</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Loss of Smell</t>
+          <t>Loss of Hearing</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>flu_symptoms_choices</t>
+          <t>recent_exposure_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>loss_of_hearing</t>
+          <t>close_contact_with_someone_who_has_influenza</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Loss of Hearing</t>
+          <t>Close contact with someone who has influenza</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>close_contact_with_someone_who_has_influenza</t>
+          <t>close_contact_with_someone_who_has_a_flu-like_illness</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Close contact with someone who has influenza</t>
+          <t>Close contact with someone who has a flu-like illness</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>close_contact_with_someone_who_has_a_flu-like_illness</t>
+          <t>close_contact_with_someone_who_has_a_different_illness</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Close contact with someone who has a flu-like illness</t>
+          <t>Close contact with someone who has a different illness</t>
         </is>
       </c>
     </row>
@@ -1590,29 +1590,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>close_contact_with_someone_who_has_a_different_illness</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Close contact with someone who has a different illness</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>recent_exposure_choices</t>
+          <t>exposure_duration_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>less_than_1_day</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Less than 1 day</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>less_than_1_day</t>
+          <t>1-2_days</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Less than 1 day</t>
+          <t>1-2 days</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1-2_days</t>
+          <t>2-5_days</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1-2 days</t>
+          <t>2-5 days</t>
         </is>
       </c>
     </row>
@@ -1658,29 +1658,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2-5_days</t>
+          <t>more_than_5_days</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2-5 days</t>
+          <t>More than 5 days</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>exposure_duration_choices</t>
+          <t>recent_contact_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>more_than_5_days</t>
+          <t>health_care_worker</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>More than 5 days</t>
+          <t>Health Care Worker</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>health_care_worker</t>
+          <t>international_traveler</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Health Care Worker</t>
+          <t>International Traveler</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>international_traveler</t>
+          <t>family_member</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>International Traveler</t>
+          <t>Family Member</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>family_member</t>
+          <t>friend/neighbor</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Family Member</t>
+          <t>Friend/Neighbor</t>
         </is>
       </c>
     </row>
@@ -1743,29 +1743,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>friend/neighbor</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Friend/Neighbor</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>recent_contact_choices</t>
+          <t>flu_vaccine_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>received_flu_vaccine_this_season</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Received flu vaccine this season</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>received_flu_vaccine_this_season</t>
+          <t>not_received_flu_vaccine_this_season</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Received flu vaccine this season</t>
+          <t>Not received flu vaccine this season</t>
         </is>
       </c>
     </row>
@@ -1794,29 +1794,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>not_received_flu_vaccine_this_season</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Not received flu vaccine this season</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>flu_vaccine_choices</t>
+          <t>healthcare_worker_contact_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1828,29 +1828,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>healthcare_worker_contact_choices</t>
+          <t>flu_symptoms_duration_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>less_than_48_hours</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Less than 48 hours</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>less_than_48_hours</t>
+          <t>48_hours_to_4_days</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Less than 48 hours</t>
+          <t>48 hours to 4 days</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>48_hours_to_4_days</t>
+          <t>5-7_days</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>48 hours to 4 days</t>
+          <t>5-7 days</t>
         </is>
       </c>
     </row>
@@ -1896,29 +1896,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5-7_days</t>
+          <t>more_than_7_days</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>5-7 days</t>
+          <t>More than 7 days</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>flu_symptoms_duration_choices</t>
+          <t>healthcare_workplace_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>more_than_7_days</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>More than 7 days</t>
+          <t>Hospital</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>hospital_emergency_room</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Hospital Emergency Room</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>hospital_emergency_room</t>
+          <t>hospital_icu</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hospital Emergency Room</t>
+          <t>Hospital ICU</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>hospital_icu</t>
+          <t>hospital_clinic</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hospital ICU</t>
+          <t>Hospital Clinic</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>hospital_clinic</t>
+          <t>hospital_nursing_home</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hospital Clinic</t>
+          <t>Hospital Nursing Home</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>hospital_nursing_home</t>
+          <t>hospital_rehabilitation_center</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hospital Nursing Home</t>
+          <t>Hospital Rehabilitation Center</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>hospital_rehabilitation_center</t>
+          <t>hospital_long-term_care</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hospital Rehabilitation Center</t>
+          <t>Hospital Long-term care</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>hospital_long-term_care</t>
+          <t>outpatient_clinic</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hospital Long-term care</t>
+          <t>Outpatient clinic</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>outpatient_clinic</t>
+          <t>long-term_care_center</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Outpatient clinic</t>
+          <t>Long-term care center</t>
         </is>
       </c>
     </row>
@@ -2066,301 +2066,301 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>long-term_care_center</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Long-term care center</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>healthcare_workplace_choices</t>
+          <t>flu_symptoms_2_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>fever</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Fever</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>flu_symptoms_choices</t>
+          <t>flu_symptoms_2_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>fever</t>
+          <t>cough</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Fever</t>
+          <t>Cough</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>flu_symptoms_choices</t>
+          <t>flu_symptoms_2_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>cough</t>
+          <t>sore_throat</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cough</t>
+          <t>Sore Throat</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>flu_symptoms_choices</t>
+          <t>flu_symptoms_2_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>sore_throat</t>
+          <t>runny_nose</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sore Throat</t>
+          <t>Runny Nose</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>flu_symptoms_choices</t>
+          <t>flu_symptoms_2_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>runny_nose</t>
+          <t>fatigue</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Runny Nose</t>
+          <t>Fatigue</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>flu_symptoms_choices</t>
+          <t>flu_symptoms_2_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>fatigue</t>
+          <t>chills</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Fatigue</t>
+          <t>Chills</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>flu_symptoms_choices</t>
+          <t>flu_symptoms_2_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>chills</t>
+          <t>muscle_aches</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chills</t>
+          <t>Muscle Aches</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>flu_symptoms_choices</t>
+          <t>flu_symptoms_2_choices</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>muscle_aches</t>
+          <t>headache</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Muscle Aches</t>
+          <t>Headache</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>flu_symptoms_choices</t>
+          <t>flu_symptoms_2_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>headache</t>
+          <t>nausea/vomiting</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Headache</t>
+          <t>Nausea/Vomiting</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>flu_symptoms_choices</t>
+          <t>flu_symptoms_2_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>sore_throat</t>
+          <t>diarrhea</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sore Throat</t>
+          <t>Diarrhea</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>flu_symptoms_choices</t>
+          <t>flu_symptoms_2_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nausea/vomiting</t>
+          <t>confusion/disorientation</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Nausea/Vomiting</t>
+          <t>Confusion/Disorientation</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>flu_symptoms_choices</t>
+          <t>flu_symptoms_2_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>diarrhea</t>
+          <t>loss_of_appetite</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Diarrhea</t>
+          <t>Loss of Appetite</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>flu_symptoms_choices</t>
+          <t>flu_symptoms_2_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>confusion/disorientation</t>
+          <t>loss_of_taste</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Confusion/Disorientation</t>
+          <t>Loss of Taste</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>flu_symptoms_choices</t>
+          <t>flu_symptoms_2_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>loss_of_appetite</t>
+          <t>loss_of_smell</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Loss of Appetite</t>
+          <t>Loss of Smell</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>flu_symptoms_choices</t>
+          <t>flu_symptoms_2_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>loss_of_taste</t>
+          <t>loss_of_hearing</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Loss of Taste</t>
+          <t>Loss of Hearing</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>flu_symptoms_choices</t>
+          <t>flu_exposure_risk_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>loss_of_smell</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Loss of Smell</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>flu_symptoms_choices</t>
+          <t>flu_exposure_risk_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>loss_of_hearing</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Loss of Hearing</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -2372,12 +2372,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2389,53 +2389,53 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>flu_exposure_risk_choices</t>
+          <t>healthcare_workplace_contact_choices</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>flu_exposure_risk_choices</t>
+          <t>healthcare_workplace_contact_choices</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>healthcare_workplace_contact_choices</t>
+          <t>healthcare_workplace_2_choices</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2452,7 +2452,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>healthcare_workplace_contact_choices</t>
+          <t>healthcare_workplace_2_choices</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2469,34 +2469,34 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>healthcare_workplace_choices</t>
+          <t>healthcare_workplace_type_choices</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>doctor/nurse</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Doctor/Nurse</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>healthcare_workplace_choices</t>
+          <t>healthcare_workplace_type_choices</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>hospital_worker</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Hospital Worker</t>
         </is>
       </c>
     </row>
@@ -2508,12 +2508,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>doctor/nurse</t>
+          <t>clinic_worker</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Doctor/Nurse</t>
+          <t>Clinic Worker</t>
         </is>
       </c>
     </row>
@@ -2525,12 +2525,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>hospital_worker</t>
+          <t>nursing_home_worker</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Hospital Worker</t>
+          <t>Nursing Home Worker</t>
         </is>
       </c>
     </row>
@@ -2542,12 +2542,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>clinic_worker</t>
+          <t>rehabilitation_worker</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Clinic Worker</t>
+          <t>Rehabilitation Worker</t>
         </is>
       </c>
     </row>
@@ -2559,80 +2559,80 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>nursing_home_worker</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Nursing Home Worker</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>healthcare_workplace_type_choices</t>
+          <t>recent_flu_exposure_choices</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>rehabilitation_worker</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Rehabilitation Worker</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>healthcare_workplace_type_choices</t>
+          <t>recent_flu_exposure_choices</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>recent_flu_exposure_choices</t>
+          <t>flu_symptoms_severity_choices</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>recent_flu_exposure_choices</t>
+          <t>flu_symptoms_severity_choices</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>mild</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -2644,12 +2644,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -2661,46 +2661,46 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>mild</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Mild</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>flu_symptoms_severity_choices</t>
+          <t>recent_flu_symptoms_choices</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>flu_symptoms_severity_choices</t>
+          <t>recent_flu_symptoms_choices</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>severe</t>
+          <t>mild</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -2712,12 +2712,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -2729,80 +2729,80 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>mild</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Mild</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>recent_flu_symptoms_choices</t>
+          <t>healthcare_worker_flu_exposure_choices</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>recent_flu_symptoms_choices</t>
+          <t>healthcare_worker_flu_exposure_choices</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>severe</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Severe</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>healthcare_worker_flu_exposure_choices</t>
+          <t>flu_vaccination_choices</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>received_flu_vaccine_this_season</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Received flu vaccine this season</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>healthcare_worker_flu_exposure_choices</t>
+          <t>flu_vaccination_choices</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>not_received_flu_vaccine_this_season</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Not received flu vaccine this season</t>
         </is>
       </c>
     </row>
@@ -2814,46 +2814,46 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>received_flu_vaccine_this_season</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Received flu vaccine this season</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>flu_vaccination_choices</t>
+          <t>healthcare_worker_flu_symptoms_choices</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>not_received_flu_vaccine_this_season</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Not received flu vaccine this season</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>flu_vaccination_choices</t>
+          <t>healthcare_worker_flu_symptoms_choices</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mild</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -2882,80 +2882,80 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>mild</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Mild</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>healthcare_worker_flu_symptoms_choices</t>
+          <t>healthcare_worker_flu_status_choices</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>healthcare_worker_flu_symptoms_choices</t>
+          <t>healthcare_worker_flu_status_choices</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>severe</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Severe</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>healthcare_worker_flu_status_choices</t>
+          <t>flu_exposure_source_choices</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>health_care_worker</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Health Care Worker</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>healthcare_worker_flu_status_choices</t>
+          <t>flu_exposure_source_choices</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>family_member</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Family Member</t>
         </is>
       </c>
     </row>
@@ -2967,12 +2967,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>health_care_worker</t>
+          <t>friend/neighbor</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Health Care Worker</t>
+          <t>Friend/Neighbor</t>
         </is>
       </c>
     </row>
@@ -2984,12 +2984,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>family_member</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Family Member</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -3001,44 +3001,10 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>friend/neighbor</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
-        <is>
-          <t>Friend/Neighbor</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>flu_exposure_source_choices</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>flu_exposure_source_choices</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
